--- a/sorted_dfs.xlsx
+++ b/sorted_dfs.xlsx
@@ -478,7 +478,7 @@
         <v>8.805999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
         <v>29.41</v>
